--- a/Kyrsach2WINFORM/TemplateDontDelete.xlsx
+++ b/Kyrsach2WINFORM/TemplateDontDelete.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\stud\Диплом\Диплом\Документы\Kyrsach2WINFORM-master\Kyrsach2WINFORM\Kyrsach2WINFORM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FBCF59D-F4F2-43A6-8F69-1E5F08AA516B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921DD90D-AFA2-42E1-96F5-F255224A99E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="285" windowWidth="30600" windowHeight="20595" xr2:uid="{66FBA5D8-FC85-4F68-9775-AD5719E334F1}"/>
+    <workbookView xWindow="2820" yWindow="1620" windowWidth="31440" windowHeight="18420" xr2:uid="{66FBA5D8-FC85-4F68-9775-AD5719E334F1}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -1043,16 +1043,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>4763</xdr:rowOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>185738</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
